--- a/assets/suivi-devis-modele-fr.xlsx
+++ b/assets/suivi-devis-modele-fr.xlsx
@@ -139,7 +139,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;$&quot;"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">

--- a/assets/suivi-devis-modele-fr.xlsx
+++ b/assets/suivi-devis-modele-fr.xlsx
@@ -25,13 +25,13 @@
     <t>Devis acceptés</t>
   </si>
   <si>
-    <t>Montant total TTC</t>
+    <t>Montant total taxes incluses</t>
   </si>
   <si>
     <t>En attente</t>
   </si>
   <si>
-    <t>Montant accepté TTC</t>
+    <t>Montant accepté taxes incluses</t>
   </si>
   <si>
     <t>Refusés</t>
@@ -49,13 +49,13 @@
     <t>Validité (jours)</t>
   </si>
   <si>
-    <t>Montant HT</t>
-  </si>
-  <si>
-    <t>TVA</t>
-  </si>
-  <si>
-    <t>Montant TTC</t>
+    <t>Montant avant taxes</t>
+  </si>
+  <si>
+    <t>Taxes</t>
+  </si>
+  <si>
+    <t>Montant taxes incluses</t>
   </si>
   <si>
     <t>Date limite</t>
@@ -137,10 +137,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;$&quot;"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="0.0##%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -203,7 +204,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -613,7 +614,7 @@
       </c>
       <c r="E4" s="4">
         <f>SUM(G8:G17)</f>
-        <v>17349.1</v>
+        <v>16731.959125</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -629,7 +630,7 @@
       </c>
       <c r="E5" s="4">
         <f>SUMIF(I8:I17,K8,G8:G17)</f>
-        <v>4630.9</v>
+        <v>4546.33375</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -690,11 +691,11 @@
         <v>2440</v>
       </c>
       <c r="F8" s="9">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="G8" s="8">
         <f>E8*(1+F8)</f>
-        <v>2928</v>
+        <v>2805.3900000000003</v>
       </c>
       <c r="H8" s="7">
         <f>C8+D8</f>
@@ -724,11 +725,11 @@
         <v>1265</v>
       </c>
       <c r="F9" s="9">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="G9" s="8">
         <f>E9*(1+F9)</f>
-        <v>1518</v>
+        <v>1454.4337500000001</v>
       </c>
       <c r="H9" s="7">
         <f>C9+D9</f>
@@ -758,11 +759,11 @@
         <v>1890</v>
       </c>
       <c r="F10" s="9">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="8">
         <f>E10*(1+F10)</f>
-        <v>2079</v>
+        <v>1984.5</v>
       </c>
       <c r="H10" s="7">
         <f>C10+D10</f>
@@ -792,11 +793,11 @@
         <v>246</v>
       </c>
       <c r="F11" s="9">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="G11" s="8">
         <f>E11*(1+F11)</f>
-        <v>295.2</v>
+        <v>282.8385</v>
       </c>
       <c r="H11" s="7">
         <f>C11+D11</f>
@@ -823,11 +824,11 @@
         <v>452.5</v>
       </c>
       <c r="F12" s="9">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="G12" s="8">
         <f>E12*(1+F12)</f>
-        <v>543</v>
+        <v>520.261875</v>
       </c>
       <c r="H12" s="7">
         <f>C12+D12</f>
@@ -854,11 +855,11 @@
         <v>3200</v>
       </c>
       <c r="F13" s="9">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="G13" s="8">
         <f>E13*(1+F13)</f>
-        <v>3840</v>
+        <v>3679.2000000000003</v>
       </c>
       <c r="H13" s="7">
         <f>C13+D13</f>
@@ -885,11 +886,11 @@
         <v>980</v>
       </c>
       <c r="F14" s="9">
-        <v>0.055</v>
+        <v>0.13</v>
       </c>
       <c r="G14" s="8">
         <f>E14*(1+F14)</f>
-        <v>1033.8999999999999</v>
+        <v>1107.3999999999999</v>
       </c>
       <c r="H14" s="7">
         <f>C14+D14</f>
@@ -916,11 +917,11 @@
         <v>1500</v>
       </c>
       <c r="F15" s="9">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="G15" s="8">
         <f>E15*(1+F15)</f>
-        <v>1800</v>
+        <v>1724.625</v>
       </c>
       <c r="H15" s="7">
         <f>C15+D15</f>
@@ -947,11 +948,11 @@
         <v>610</v>
       </c>
       <c r="F16" s="9">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="G16" s="8">
         <f>E16*(1+F16)</f>
-        <v>732</v>
+        <v>701.3475000000001</v>
       </c>
       <c r="H16" s="7">
         <f>C16+D16</f>
@@ -978,11 +979,11 @@
         <v>2150</v>
       </c>
       <c r="F17" s="9">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
       <c r="G17" s="8">
         <f>E17*(1+F17)</f>
-        <v>2580</v>
+        <v>2471.9625</v>
       </c>
       <c r="H17" s="7">
         <f>C17+D17</f>
